--- a/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
+++ b/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
@@ -1120,7 +1120,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Drop this sheet into the model, then Calculate (Ctrl+Alt+F9). Blue cells are live formulas against HDUnitLevel, T12 Dump, RRA, tblRentRoll and Cash Flow (Annual). Grey cells are static reconstructed history — the model has no equivalent source for them.</t>
+          <t>Drop this sheet into the model, then Calculate (Ctrl+Alt+F9). Blue cells are live formulas against HD Dump, T12 Dump, RRA, RR Dump and Cash Flow (Annual). Grey cells are static reconstructed history — the model has no equivalent source for them.</t>
         </is>
       </c>
     </row>
@@ -1197,39 +1197,39 @@
         </is>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],C7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,C7)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],D7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,D7)</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],E7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,E7)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],F7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,F7)</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],G7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,G7)</f>
         <v/>
       </c>
       <c r="H8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],H7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,H7)</f>
         <v/>
       </c>
       <c r="I8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],I7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,I7)</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],J7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,J7)</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>COUNTIFS(tblRentRoll[Floor Plan],K7)</f>
+        <f>COUNTIFS('RR Dump'!$B$2:$B$361,K7)</f>
         <v/>
       </c>
       <c r="L8" s="7">
@@ -1374,75 +1374,75 @@
       <c r="O11" s="17" t="n"/>
       <c r="P11" s="11" t="n"/>
       <c r="T11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="U11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="V11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="W11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="X11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="Y11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="Z11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AA11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AB11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AD11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AE11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AF11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AG11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AH11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AI11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AJ11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AK11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
       <c r="AL11" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B11-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B11),"")</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B11-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B11),"")</f>
         <v/>
       </c>
     </row>
@@ -1486,75 +1486,75 @@
       <c r="O12" s="17" t="n"/>
       <c r="P12" s="11" t="n"/>
       <c r="T12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),T11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),T11)</f>
         <v/>
       </c>
       <c r="U12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),U11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),U11)</f>
         <v/>
       </c>
       <c r="V12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),V11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),V11)</f>
         <v/>
       </c>
       <c r="W12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),W11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),W11)</f>
         <v/>
       </c>
       <c r="X12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),X11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),X11)</f>
         <v/>
       </c>
       <c r="Y12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),Y11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),Y11)</f>
         <v/>
       </c>
       <c r="Z12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),Z11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),Z11)</f>
         <v/>
       </c>
       <c r="AA12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AA11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AA11)</f>
         <v/>
       </c>
       <c r="AB12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AB11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AB11)</f>
         <v/>
       </c>
       <c r="AD12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AD11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AD11)</f>
         <v/>
       </c>
       <c r="AE12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AE11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AE11)</f>
         <v/>
       </c>
       <c r="AF12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AF11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AF11)</f>
         <v/>
       </c>
       <c r="AG12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AG11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AG11)</f>
         <v/>
       </c>
       <c r="AH12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AH11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AH11)</f>
         <v/>
       </c>
       <c r="AI12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AI11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AI11)</f>
         <v/>
       </c>
       <c r="AJ12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AJ11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AJ11)</f>
         <v/>
       </c>
       <c r="AK12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AK11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AK11)</f>
         <v/>
       </c>
       <c r="AL12" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B12-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B12),AL11)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B12-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B12),AL11)</f>
         <v/>
       </c>
     </row>
@@ -1598,75 +1598,75 @@
       <c r="O13" s="17" t="n"/>
       <c r="P13" s="11" t="n"/>
       <c r="T13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),T12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),T12)</f>
         <v/>
       </c>
       <c r="U13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),U12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),U12)</f>
         <v/>
       </c>
       <c r="V13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),V12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),V12)</f>
         <v/>
       </c>
       <c r="W13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),W12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),W12)</f>
         <v/>
       </c>
       <c r="X13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),X12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),X12)</f>
         <v/>
       </c>
       <c r="Y13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),Y12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),Y12)</f>
         <v/>
       </c>
       <c r="Z13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),Z12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),Z12)</f>
         <v/>
       </c>
       <c r="AA13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AA12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AA12)</f>
         <v/>
       </c>
       <c r="AB13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AB12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AB12)</f>
         <v/>
       </c>
       <c r="AD13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AD12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AD12)</f>
         <v/>
       </c>
       <c r="AE13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AE12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AE12)</f>
         <v/>
       </c>
       <c r="AF13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AF12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AF12)</f>
         <v/>
       </c>
       <c r="AG13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AG12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AG12)</f>
         <v/>
       </c>
       <c r="AH13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AH12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AH12)</f>
         <v/>
       </c>
       <c r="AI13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AI12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AI12)</f>
         <v/>
       </c>
       <c r="AJ13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AJ12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AJ12)</f>
         <v/>
       </c>
       <c r="AK13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AK12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AK12)</f>
         <v/>
       </c>
       <c r="AL13" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B13-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B13),AL12)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B13-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B13),AL12)</f>
         <v/>
       </c>
     </row>
@@ -1710,75 +1710,75 @@
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="11" t="n"/>
       <c r="T14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),T13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),T13)</f>
         <v/>
       </c>
       <c r="U14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),U13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),U13)</f>
         <v/>
       </c>
       <c r="V14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),V13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),V13)</f>
         <v/>
       </c>
       <c r="W14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),W13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),W13)</f>
         <v/>
       </c>
       <c r="X14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),X13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),X13)</f>
         <v/>
       </c>
       <c r="Y14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),Y13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),Y13)</f>
         <v/>
       </c>
       <c r="Z14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),Z13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),Z13)</f>
         <v/>
       </c>
       <c r="AA14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AA13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AA13)</f>
         <v/>
       </c>
       <c r="AB14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AB13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AB13)</f>
         <v/>
       </c>
       <c r="AD14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AD13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AD13)</f>
         <v/>
       </c>
       <c r="AE14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AE13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AE13)</f>
         <v/>
       </c>
       <c r="AF14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AF13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AF13)</f>
         <v/>
       </c>
       <c r="AG14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AG13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AG13)</f>
         <v/>
       </c>
       <c r="AH14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AH13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AH13)</f>
         <v/>
       </c>
       <c r="AI14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AI13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AI13)</f>
         <v/>
       </c>
       <c r="AJ14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AJ13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AJ13)</f>
         <v/>
       </c>
       <c r="AK14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AK13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AK13)</f>
         <v/>
       </c>
       <c r="AL14" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B14-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B14),AL13)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B14-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B14),AL13)</f>
         <v/>
       </c>
     </row>
@@ -1822,75 +1822,75 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="11" t="n"/>
       <c r="T15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),T14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),T14)</f>
         <v/>
       </c>
       <c r="U15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),U14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),U14)</f>
         <v/>
       </c>
       <c r="V15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),V14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),V14)</f>
         <v/>
       </c>
       <c r="W15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),W14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),W14)</f>
         <v/>
       </c>
       <c r="X15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),X14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),X14)</f>
         <v/>
       </c>
       <c r="Y15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),Y14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),Y14)</f>
         <v/>
       </c>
       <c r="Z15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),Z14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),Z14)</f>
         <v/>
       </c>
       <c r="AA15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AA14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AA14)</f>
         <v/>
       </c>
       <c r="AB15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AB14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AB14)</f>
         <v/>
       </c>
       <c r="AD15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AD14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AD14)</f>
         <v/>
       </c>
       <c r="AE15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AE14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AE14)</f>
         <v/>
       </c>
       <c r="AF15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AF14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AF14)</f>
         <v/>
       </c>
       <c r="AG15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AG14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AG14)</f>
         <v/>
       </c>
       <c r="AH15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AH14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AH14)</f>
         <v/>
       </c>
       <c r="AI15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AI14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AI14)</f>
         <v/>
       </c>
       <c r="AJ15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AJ14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AJ14)</f>
         <v/>
       </c>
       <c r="AK15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AK14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AK14)</f>
         <v/>
       </c>
       <c r="AL15" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B15-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B15),AL14)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B15-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B15),AL14)</f>
         <v/>
       </c>
     </row>
@@ -1934,75 +1934,75 @@
       <c r="O16" s="17" t="n"/>
       <c r="P16" s="11" t="n"/>
       <c r="T16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),T15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),T15)</f>
         <v/>
       </c>
       <c r="U16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),U15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),U15)</f>
         <v/>
       </c>
       <c r="V16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),V15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),V15)</f>
         <v/>
       </c>
       <c r="W16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),W15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),W15)</f>
         <v/>
       </c>
       <c r="X16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),X15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),X15)</f>
         <v/>
       </c>
       <c r="Y16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),Y15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),Y15)</f>
         <v/>
       </c>
       <c r="Z16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),Z15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),Z15)</f>
         <v/>
       </c>
       <c r="AA16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AA15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AA15)</f>
         <v/>
       </c>
       <c r="AB16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AB15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AB15)</f>
         <v/>
       </c>
       <c r="AD16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AD15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AD15)</f>
         <v/>
       </c>
       <c r="AE16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AE15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AE15)</f>
         <v/>
       </c>
       <c r="AF16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AF15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AF15)</f>
         <v/>
       </c>
       <c r="AG16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AG15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AG15)</f>
         <v/>
       </c>
       <c r="AH16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AH15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AH15)</f>
         <v/>
       </c>
       <c r="AI16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AI15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AI15)</f>
         <v/>
       </c>
       <c r="AJ16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AJ15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AJ15)</f>
         <v/>
       </c>
       <c r="AK16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AK15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AK15)</f>
         <v/>
       </c>
       <c r="AL16" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B16-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B16),AL15)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B16-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B16),AL15)</f>
         <v/>
       </c>
     </row>
@@ -2046,75 +2046,75 @@
       <c r="O17" s="17" t="n"/>
       <c r="P17" s="11" t="n"/>
       <c r="T17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),T16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),T16)</f>
         <v/>
       </c>
       <c r="U17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),U16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),U16)</f>
         <v/>
       </c>
       <c r="V17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),V16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),V16)</f>
         <v/>
       </c>
       <c r="W17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),W16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),W16)</f>
         <v/>
       </c>
       <c r="X17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),X16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),X16)</f>
         <v/>
       </c>
       <c r="Y17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),Y16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),Y16)</f>
         <v/>
       </c>
       <c r="Z17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),Z16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),Z16)</f>
         <v/>
       </c>
       <c r="AA17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AA16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AA16)</f>
         <v/>
       </c>
       <c r="AB17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AB16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AB16)</f>
         <v/>
       </c>
       <c r="AD17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AD16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AD16)</f>
         <v/>
       </c>
       <c r="AE17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AE16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AE16)</f>
         <v/>
       </c>
       <c r="AF17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AF16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AF16)</f>
         <v/>
       </c>
       <c r="AG17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AG16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AG16)</f>
         <v/>
       </c>
       <c r="AH17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AH16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AH16)</f>
         <v/>
       </c>
       <c r="AI17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AI16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AI16)</f>
         <v/>
       </c>
       <c r="AJ17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AJ16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AJ16)</f>
         <v/>
       </c>
       <c r="AK17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AK16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AK16)</f>
         <v/>
       </c>
       <c r="AL17" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B17-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B17),AL16)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B17-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B17),AL16)</f>
         <v/>
       </c>
     </row>
@@ -2158,75 +2158,75 @@
       <c r="O18" s="17" t="n"/>
       <c r="P18" s="11" t="n"/>
       <c r="T18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),T17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),T17)</f>
         <v/>
       </c>
       <c r="U18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),U17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),U17)</f>
         <v/>
       </c>
       <c r="V18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),V17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),V17)</f>
         <v/>
       </c>
       <c r="W18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),W17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),W17)</f>
         <v/>
       </c>
       <c r="X18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),X17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),X17)</f>
         <v/>
       </c>
       <c r="Y18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),Y17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),Y17)</f>
         <v/>
       </c>
       <c r="Z18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),Z17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),Z17)</f>
         <v/>
       </c>
       <c r="AA18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AA17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AA17)</f>
         <v/>
       </c>
       <c r="AB18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AB17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AB17)</f>
         <v/>
       </c>
       <c r="AD18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AD17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AD17)</f>
         <v/>
       </c>
       <c r="AE18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AE17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AE17)</f>
         <v/>
       </c>
       <c r="AF18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AF17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AF17)</f>
         <v/>
       </c>
       <c r="AG18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AG17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AG17)</f>
         <v/>
       </c>
       <c r="AH18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AH17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AH17)</f>
         <v/>
       </c>
       <c r="AI18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AI17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AI17)</f>
         <v/>
       </c>
       <c r="AJ18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AJ17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AJ17)</f>
         <v/>
       </c>
       <c r="AK18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AK17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AK17)</f>
         <v/>
       </c>
       <c r="AL18" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B18-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B18),AL17)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B18-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B18),AL17)</f>
         <v/>
       </c>
     </row>
@@ -2270,75 +2270,75 @@
       <c r="O19" s="17" t="n"/>
       <c r="P19" s="11" t="n"/>
       <c r="T19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),T18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),T18)</f>
         <v/>
       </c>
       <c r="U19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),U18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),U18)</f>
         <v/>
       </c>
       <c r="V19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),V18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),V18)</f>
         <v/>
       </c>
       <c r="W19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),W18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),W18)</f>
         <v/>
       </c>
       <c r="X19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),X18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),X18)</f>
         <v/>
       </c>
       <c r="Y19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),Y18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),Y18)</f>
         <v/>
       </c>
       <c r="Z19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),Z18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),Z18)</f>
         <v/>
       </c>
       <c r="AA19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AA18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AA18)</f>
         <v/>
       </c>
       <c r="AB19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AB18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AB18)</f>
         <v/>
       </c>
       <c r="AD19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AD18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AD18)</f>
         <v/>
       </c>
       <c r="AE19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AE18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AE18)</f>
         <v/>
       </c>
       <c r="AF19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AF18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AF18)</f>
         <v/>
       </c>
       <c r="AG19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AG18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AG18)</f>
         <v/>
       </c>
       <c r="AH19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AH18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AH18)</f>
         <v/>
       </c>
       <c r="AI19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AI18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AI18)</f>
         <v/>
       </c>
       <c r="AJ19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AJ18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AJ18)</f>
         <v/>
       </c>
       <c r="AK19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AK18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AK18)</f>
         <v/>
       </c>
       <c r="AL19" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B19-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B19),AL18)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B19-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B19),AL18)</f>
         <v/>
       </c>
     </row>
@@ -2382,75 +2382,75 @@
       <c r="O20" s="17" t="n"/>
       <c r="P20" s="11" t="n"/>
       <c r="T20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),T19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),T19)</f>
         <v/>
       </c>
       <c r="U20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),U19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),U19)</f>
         <v/>
       </c>
       <c r="V20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),V19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),V19)</f>
         <v/>
       </c>
       <c r="W20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),W19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),W19)</f>
         <v/>
       </c>
       <c r="X20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),X19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),X19)</f>
         <v/>
       </c>
       <c r="Y20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),Y19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),Y19)</f>
         <v/>
       </c>
       <c r="Z20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),Z19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),Z19)</f>
         <v/>
       </c>
       <c r="AA20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AA19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AA19)</f>
         <v/>
       </c>
       <c r="AB20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AB19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AB19)</f>
         <v/>
       </c>
       <c r="AD20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AD19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AD19)</f>
         <v/>
       </c>
       <c r="AE20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AE19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AE19)</f>
         <v/>
       </c>
       <c r="AF20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AF19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AF19)</f>
         <v/>
       </c>
       <c r="AG20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AG19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AG19)</f>
         <v/>
       </c>
       <c r="AH20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AH19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AH19)</f>
         <v/>
       </c>
       <c r="AI20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AI19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AI19)</f>
         <v/>
       </c>
       <c r="AJ20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AJ19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AJ19)</f>
         <v/>
       </c>
       <c r="AK20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AK19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AK19)</f>
         <v/>
       </c>
       <c r="AL20" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B20-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B20),AL19)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B20-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B20),AL19)</f>
         <v/>
       </c>
     </row>
@@ -2494,75 +2494,75 @@
       <c r="O21" s="17" t="n"/>
       <c r="P21" s="11" t="n"/>
       <c r="T21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),T20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),T20)</f>
         <v/>
       </c>
       <c r="U21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),U20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),U20)</f>
         <v/>
       </c>
       <c r="V21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),V20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),V20)</f>
         <v/>
       </c>
       <c r="W21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),W20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),W20)</f>
         <v/>
       </c>
       <c r="X21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),X20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),X20)</f>
         <v/>
       </c>
       <c r="Y21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),Y20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),Y20)</f>
         <v/>
       </c>
       <c r="Z21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),Z20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),Z20)</f>
         <v/>
       </c>
       <c r="AA21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AA20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AA20)</f>
         <v/>
       </c>
       <c r="AB21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AB20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AB20)</f>
         <v/>
       </c>
       <c r="AD21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AD20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AD20)</f>
         <v/>
       </c>
       <c r="AE21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AE20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AE20)</f>
         <v/>
       </c>
       <c r="AF21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AF20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AF20)</f>
         <v/>
       </c>
       <c r="AG21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AG20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AG20)</f>
         <v/>
       </c>
       <c r="AH21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AH20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AH20)</f>
         <v/>
       </c>
       <c r="AI21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AI20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AI20)</f>
         <v/>
       </c>
       <c r="AJ21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AJ20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AJ20)</f>
         <v/>
       </c>
       <c r="AK21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AK20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AK20)</f>
         <v/>
       </c>
       <c r="AL21" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B21-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B21),AL20)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B21-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B21),AL20)</f>
         <v/>
       </c>
     </row>
@@ -2606,75 +2606,75 @@
       <c r="O22" s="17" t="n"/>
       <c r="P22" s="11" t="n"/>
       <c r="T22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),T21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),T21)</f>
         <v/>
       </c>
       <c r="U22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),U21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),U21)</f>
         <v/>
       </c>
       <c r="V22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),V21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),V21)</f>
         <v/>
       </c>
       <c r="W22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),W21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),W21)</f>
         <v/>
       </c>
       <c r="X22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),X21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),X21)</f>
         <v/>
       </c>
       <c r="Y22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),Y21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),Y21)</f>
         <v/>
       </c>
       <c r="Z22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),Z21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),Z21)</f>
         <v/>
       </c>
       <c r="AA22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AA21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AA21)</f>
         <v/>
       </c>
       <c r="AB22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AB21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AB21)</f>
         <v/>
       </c>
       <c r="AD22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AD21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AD21)</f>
         <v/>
       </c>
       <c r="AE22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AE21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AE21)</f>
         <v/>
       </c>
       <c r="AF22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AF21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AF21)</f>
         <v/>
       </c>
       <c r="AG22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AG21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AG21)</f>
         <v/>
       </c>
       <c r="AH22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AH21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AH21)</f>
         <v/>
       </c>
       <c r="AI22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AI21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AI21)</f>
         <v/>
       </c>
       <c r="AJ22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AJ21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AJ21)</f>
         <v/>
       </c>
       <c r="AK22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AK21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AK21)</f>
         <v/>
       </c>
       <c r="AL22" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B22-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B22),AL21)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B22-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B22),AL21)</f>
         <v/>
       </c>
     </row>
@@ -2718,75 +2718,75 @@
       <c r="O23" s="17" t="n"/>
       <c r="P23" s="11" t="n"/>
       <c r="T23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),T22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),T22)</f>
         <v/>
       </c>
       <c r="U23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),U22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),U22)</f>
         <v/>
       </c>
       <c r="V23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),V22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),V22)</f>
         <v/>
       </c>
       <c r="W23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),W22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),W22)</f>
         <v/>
       </c>
       <c r="X23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),X22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),X22)</f>
         <v/>
       </c>
       <c r="Y23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),Y22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),Y22)</f>
         <v/>
       </c>
       <c r="Z23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),Z22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),Z22)</f>
         <v/>
       </c>
       <c r="AA23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AA22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AA22)</f>
         <v/>
       </c>
       <c r="AB23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AB22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AB22)</f>
         <v/>
       </c>
       <c r="AD23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AD22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AD22)</f>
         <v/>
       </c>
       <c r="AE23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AE22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AE22)</f>
         <v/>
       </c>
       <c r="AF23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AF22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AF22)</f>
         <v/>
       </c>
       <c r="AG23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AG22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AG22)</f>
         <v/>
       </c>
       <c r="AH23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AH22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AH22)</f>
         <v/>
       </c>
       <c r="AI23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AI22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AI22)</f>
         <v/>
       </c>
       <c r="AJ23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AJ22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AJ22)</f>
         <v/>
       </c>
       <c r="AK23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AK22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AK22)</f>
         <v/>
       </c>
       <c r="AL23" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B23-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B23),AL22)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B23-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B23),AL22)</f>
         <v/>
       </c>
     </row>
@@ -2834,75 +2834,75 @@
       </c>
       <c r="P24" s="11" t="n"/>
       <c r="T24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),T23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),T23)</f>
         <v/>
       </c>
       <c r="U24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),U23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),U23)</f>
         <v/>
       </c>
       <c r="V24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),V23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),V23)</f>
         <v/>
       </c>
       <c r="W24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),W23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),W23)</f>
         <v/>
       </c>
       <c r="X24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),X23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),X23)</f>
         <v/>
       </c>
       <c r="Y24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),Y23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),Y23)</f>
         <v/>
       </c>
       <c r="Z24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),Z23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),Z23)</f>
         <v/>
       </c>
       <c r="AA24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AA23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AA23)</f>
         <v/>
       </c>
       <c r="AB24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AB23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AB23)</f>
         <v/>
       </c>
       <c r="AD24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AD23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AD23)</f>
         <v/>
       </c>
       <c r="AE24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AE23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AE23)</f>
         <v/>
       </c>
       <c r="AF24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AF23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AF23)</f>
         <v/>
       </c>
       <c r="AG24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AG23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AG23)</f>
         <v/>
       </c>
       <c r="AH24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AH23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AH23)</f>
         <v/>
       </c>
       <c r="AI24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AI23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AI23)</f>
         <v/>
       </c>
       <c r="AJ24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AJ23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AJ23)</f>
         <v/>
       </c>
       <c r="AK24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AK23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AK23)</f>
         <v/>
       </c>
       <c r="AL24" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B24-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B24),AL23)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),AL23)</f>
         <v/>
       </c>
     </row>
@@ -2946,75 +2946,75 @@
       <c r="O25" s="17" t="n"/>
       <c r="P25" s="11" t="n"/>
       <c r="T25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),T24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),T24)</f>
         <v/>
       </c>
       <c r="U25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),U24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),U24)</f>
         <v/>
       </c>
       <c r="V25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),V24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),V24)</f>
         <v/>
       </c>
       <c r="W25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),W24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),W24)</f>
         <v/>
       </c>
       <c r="X25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),X24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),X24)</f>
         <v/>
       </c>
       <c r="Y25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),Y24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),Y24)</f>
         <v/>
       </c>
       <c r="Z25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),Z24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),Z24)</f>
         <v/>
       </c>
       <c r="AA25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AA24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AA24)</f>
         <v/>
       </c>
       <c r="AB25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AB24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AB24)</f>
         <v/>
       </c>
       <c r="AD25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AD24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AD24)</f>
         <v/>
       </c>
       <c r="AE25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AE24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AE24)</f>
         <v/>
       </c>
       <c r="AF25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AF24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AF24)</f>
         <v/>
       </c>
       <c r="AG25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AG24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AG24)</f>
         <v/>
       </c>
       <c r="AH25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AH24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AH24)</f>
         <v/>
       </c>
       <c r="AI25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AI24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AI24)</f>
         <v/>
       </c>
       <c r="AJ25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AJ24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AJ24)</f>
         <v/>
       </c>
       <c r="AK25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AK24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AK24)</f>
         <v/>
       </c>
       <c r="AL25" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B25-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B25),AL24)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B25-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B25),AL24)</f>
         <v/>
       </c>
     </row>
@@ -3062,75 +3062,75 @@
       </c>
       <c r="P26" s="11" t="n"/>
       <c r="T26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),T25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),T25)</f>
         <v/>
       </c>
       <c r="U26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),U25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),U25)</f>
         <v/>
       </c>
       <c r="V26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),V25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),V25)</f>
         <v/>
       </c>
       <c r="W26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),W25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),W25)</f>
         <v/>
       </c>
       <c r="X26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),X25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),X25)</f>
         <v/>
       </c>
       <c r="Y26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),Y25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),Y25)</f>
         <v/>
       </c>
       <c r="Z26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),Z25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),Z25)</f>
         <v/>
       </c>
       <c r="AA26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AA25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AA25)</f>
         <v/>
       </c>
       <c r="AB26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AB25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AB25)</f>
         <v/>
       </c>
       <c r="AD26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AD25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AD25)</f>
         <v/>
       </c>
       <c r="AE26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AE25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AE25)</f>
         <v/>
       </c>
       <c r="AF26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AF25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AF25)</f>
         <v/>
       </c>
       <c r="AG26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AG25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AG25)</f>
         <v/>
       </c>
       <c r="AH26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AH25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AH25)</f>
         <v/>
       </c>
       <c r="AI26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AI25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AI25)</f>
         <v/>
       </c>
       <c r="AJ26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AJ25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AJ25)</f>
         <v/>
       </c>
       <c r="AK26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AK25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AK25)</f>
         <v/>
       </c>
       <c r="AL26" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B26-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B26),AL25)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),AL25)</f>
         <v/>
       </c>
     </row>
@@ -3178,75 +3178,75 @@
       </c>
       <c r="P27" s="11" t="n"/>
       <c r="T27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),T26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),T26)</f>
         <v/>
       </c>
       <c r="U27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),U26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),U26)</f>
         <v/>
       </c>
       <c r="V27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),V26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),V26)</f>
         <v/>
       </c>
       <c r="W27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),W26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),W26)</f>
         <v/>
       </c>
       <c r="X27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),X26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),X26)</f>
         <v/>
       </c>
       <c r="Y27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),Y26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),Y26)</f>
         <v/>
       </c>
       <c r="Z27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),Z26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),Z26)</f>
         <v/>
       </c>
       <c r="AA27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AA26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AA26)</f>
         <v/>
       </c>
       <c r="AB27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AB26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AB26)</f>
         <v/>
       </c>
       <c r="AD27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AD26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AD26)</f>
         <v/>
       </c>
       <c r="AE27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AE26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AE26)</f>
         <v/>
       </c>
       <c r="AF27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AF26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AF26)</f>
         <v/>
       </c>
       <c r="AG27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AG26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AG26)</f>
         <v/>
       </c>
       <c r="AH27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AH26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AH26)</f>
         <v/>
       </c>
       <c r="AI27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AI26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AI26)</f>
         <v/>
       </c>
       <c r="AJ27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AJ26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AJ26)</f>
         <v/>
       </c>
       <c r="AK27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AK26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AK26)</f>
         <v/>
       </c>
       <c r="AL27" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B27-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B27),AL26)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),AL26)</f>
         <v/>
       </c>
     </row>
@@ -3294,75 +3294,75 @@
       </c>
       <c r="P28" s="11" t="n"/>
       <c r="T28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),T27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),T27)</f>
         <v/>
       </c>
       <c r="U28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),U27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),U27)</f>
         <v/>
       </c>
       <c r="V28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),V27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),V27)</f>
         <v/>
       </c>
       <c r="W28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),W27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),W27)</f>
         <v/>
       </c>
       <c r="X28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),X27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),X27)</f>
         <v/>
       </c>
       <c r="Y28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),Y27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),Y27)</f>
         <v/>
       </c>
       <c r="Z28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),Z27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),Z27)</f>
         <v/>
       </c>
       <c r="AA28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AA27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AA27)</f>
         <v/>
       </c>
       <c r="AB28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AB27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AB27)</f>
         <v/>
       </c>
       <c r="AD28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AD27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AD27)</f>
         <v/>
       </c>
       <c r="AE28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AE27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AE27)</f>
         <v/>
       </c>
       <c r="AF28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AF27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AF27)</f>
         <v/>
       </c>
       <c r="AG28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AG27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AG27)</f>
         <v/>
       </c>
       <c r="AH28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AH27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AH27)</f>
         <v/>
       </c>
       <c r="AI28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AI27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AI27)</f>
         <v/>
       </c>
       <c r="AJ28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AJ27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AJ27)</f>
         <v/>
       </c>
       <c r="AK28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AK27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AK27)</f>
         <v/>
       </c>
       <c r="AL28" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B28-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B28),AL27)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),AL27)</f>
         <v/>
       </c>
     </row>
@@ -3412,75 +3412,75 @@
       </c>
       <c r="P29" s="11" t="n"/>
       <c r="T29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),T28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),T28)</f>
         <v/>
       </c>
       <c r="U29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),U28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),U28)</f>
         <v/>
       </c>
       <c r="V29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),V28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),V28)</f>
         <v/>
       </c>
       <c r="W29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),W28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),W28)</f>
         <v/>
       </c>
       <c r="X29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),X28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),X28)</f>
         <v/>
       </c>
       <c r="Y29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),Y28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),Y28)</f>
         <v/>
       </c>
       <c r="Z29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),Z28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),Z28)</f>
         <v/>
       </c>
       <c r="AA29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AA28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AA28)</f>
         <v/>
       </c>
       <c r="AB29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AB28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AB28)</f>
         <v/>
       </c>
       <c r="AD29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AD28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AD28)</f>
         <v/>
       </c>
       <c r="AE29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AE28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AE28)</f>
         <v/>
       </c>
       <c r="AF29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AF28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AF28)</f>
         <v/>
       </c>
       <c r="AG29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AG28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AG28)</f>
         <v/>
       </c>
       <c r="AH29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AH28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AH28)</f>
         <v/>
       </c>
       <c r="AI29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AI28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AI28)</f>
         <v/>
       </c>
       <c r="AJ29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AJ28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AJ28)</f>
         <v/>
       </c>
       <c r="AK29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AK28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AK28)</f>
         <v/>
       </c>
       <c r="AL29" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B29-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B29),AL28)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B29-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B29),AL28)</f>
         <v/>
       </c>
     </row>
@@ -3530,75 +3530,75 @@
       </c>
       <c r="P30" s="11" t="n"/>
       <c r="T30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),T29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),T29)</f>
         <v/>
       </c>
       <c r="U30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),U29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),U29)</f>
         <v/>
       </c>
       <c r="V30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),V29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),V29)</f>
         <v/>
       </c>
       <c r="W30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),W29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),W29)</f>
         <v/>
       </c>
       <c r="X30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),X29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),X29)</f>
         <v/>
       </c>
       <c r="Y30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),Y29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),Y29)</f>
         <v/>
       </c>
       <c r="Z30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),Z29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),Z29)</f>
         <v/>
       </c>
       <c r="AA30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AA29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AA29)</f>
         <v/>
       </c>
       <c r="AB30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AB29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AB29)</f>
         <v/>
       </c>
       <c r="AD30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AD29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AD29)</f>
         <v/>
       </c>
       <c r="AE30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AE29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AE29)</f>
         <v/>
       </c>
       <c r="AF30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AF29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AF29)</f>
         <v/>
       </c>
       <c r="AG30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AG29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AG29)</f>
         <v/>
       </c>
       <c r="AH30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AH29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AH29)</f>
         <v/>
       </c>
       <c r="AI30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AI29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AI29)</f>
         <v/>
       </c>
       <c r="AJ30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AJ29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AJ29)</f>
         <v/>
       </c>
       <c r="AK30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AK29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AK29)</f>
         <v/>
       </c>
       <c r="AL30" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B30-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B30),AL29)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B30-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B30),AL29)</f>
         <v/>
       </c>
     </row>
@@ -3648,75 +3648,75 @@
       </c>
       <c r="P31" s="11" t="n"/>
       <c r="T31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),T30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),T30)</f>
         <v/>
       </c>
       <c r="U31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),U30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),U30)</f>
         <v/>
       </c>
       <c r="V31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),V30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),V30)</f>
         <v/>
       </c>
       <c r="W31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),W30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),W30)</f>
         <v/>
       </c>
       <c r="X31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),X30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),X30)</f>
         <v/>
       </c>
       <c r="Y31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),Y30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),Y30)</f>
         <v/>
       </c>
       <c r="Z31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),Z30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),Z30)</f>
         <v/>
       </c>
       <c r="AA31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AA30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AA30)</f>
         <v/>
       </c>
       <c r="AB31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AB30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AB30)</f>
         <v/>
       </c>
       <c r="AD31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AD30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AD30)</f>
         <v/>
       </c>
       <c r="AE31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AE30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AE30)</f>
         <v/>
       </c>
       <c r="AF31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AF30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AF30)</f>
         <v/>
       </c>
       <c r="AG31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AG30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AG30)</f>
         <v/>
       </c>
       <c r="AH31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AH30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AH30)</f>
         <v/>
       </c>
       <c r="AI31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AI30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AI30)</f>
         <v/>
       </c>
       <c r="AJ31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AJ30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AJ30)</f>
         <v/>
       </c>
       <c r="AK31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AK30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AK30)</f>
         <v/>
       </c>
       <c r="AL31" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B31-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B31),AL30)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B31-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B31),AL30)</f>
         <v/>
       </c>
     </row>
@@ -3766,75 +3766,75 @@
       </c>
       <c r="P32" s="11" t="n"/>
       <c r="T32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),T31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),T31)</f>
         <v/>
       </c>
       <c r="U32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),U31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),U31)</f>
         <v/>
       </c>
       <c r="V32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),V31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),V31)</f>
         <v/>
       </c>
       <c r="W32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),W31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),W31)</f>
         <v/>
       </c>
       <c r="X32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),X31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),X31)</f>
         <v/>
       </c>
       <c r="Y32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),Y31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),Y31)</f>
         <v/>
       </c>
       <c r="Z32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),Z31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),Z31)</f>
         <v/>
       </c>
       <c r="AA32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AA31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AA31)</f>
         <v/>
       </c>
       <c r="AB32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AB31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AB31)</f>
         <v/>
       </c>
       <c r="AD32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AD31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AD31)</f>
         <v/>
       </c>
       <c r="AE32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AE31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AE31)</f>
         <v/>
       </c>
       <c r="AF32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AF31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AF31)</f>
         <v/>
       </c>
       <c r="AG32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AG31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AG31)</f>
         <v/>
       </c>
       <c r="AH32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AH31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AH31)</f>
         <v/>
       </c>
       <c r="AI32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AI31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AI31)</f>
         <v/>
       </c>
       <c r="AJ32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AJ31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AJ31)</f>
         <v/>
       </c>
       <c r="AK32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AK31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AK31)</f>
         <v/>
       </c>
       <c r="AL32" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B32-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B32),AL31)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B32-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B32),AL31)</f>
         <v/>
       </c>
     </row>
@@ -3884,75 +3884,75 @@
       </c>
       <c r="P33" s="11" t="n"/>
       <c r="T33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),T32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),T32)</f>
         <v/>
       </c>
       <c r="U33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),U32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),U32)</f>
         <v/>
       </c>
       <c r="V33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),V32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),V32)</f>
         <v/>
       </c>
       <c r="W33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),W32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),W32)</f>
         <v/>
       </c>
       <c r="X33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),X32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),X32)</f>
         <v/>
       </c>
       <c r="Y33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),Y32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),Y32)</f>
         <v/>
       </c>
       <c r="Z33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),Z32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),Z32)</f>
         <v/>
       </c>
       <c r="AA33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AA32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AA32)</f>
         <v/>
       </c>
       <c r="AB33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AB32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AB32)</f>
         <v/>
       </c>
       <c r="AD33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AD32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AD32)</f>
         <v/>
       </c>
       <c r="AE33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AE32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AE32)</f>
         <v/>
       </c>
       <c r="AF33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AF32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AF32)</f>
         <v/>
       </c>
       <c r="AG33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AG32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AG32)</f>
         <v/>
       </c>
       <c r="AH33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AH32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AH32)</f>
         <v/>
       </c>
       <c r="AI33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AI32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AI32)</f>
         <v/>
       </c>
       <c r="AJ33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AJ32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AJ32)</f>
         <v/>
       </c>
       <c r="AK33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AK32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AK32)</f>
         <v/>
       </c>
       <c r="AL33" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B33-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B33),AL32)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B33-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B33),AL32)</f>
         <v/>
       </c>
     </row>
@@ -4002,75 +4002,75 @@
       </c>
       <c r="P34" s="11" t="n"/>
       <c r="T34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),T33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),T33)</f>
         <v/>
       </c>
       <c r="U34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),U33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),U33)</f>
         <v/>
       </c>
       <c r="V34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),V33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),V33)</f>
         <v/>
       </c>
       <c r="W34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),W33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),W33)</f>
         <v/>
       </c>
       <c r="X34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),X33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),X33)</f>
         <v/>
       </c>
       <c r="Y34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),Y33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),Y33)</f>
         <v/>
       </c>
       <c r="Z34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),Z33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),Z33)</f>
         <v/>
       </c>
       <c r="AA34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AA33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AA33)</f>
         <v/>
       </c>
       <c r="AB34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AB33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AB33)</f>
         <v/>
       </c>
       <c r="AD34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AD33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AD33)</f>
         <v/>
       </c>
       <c r="AE34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AE33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AE33)</f>
         <v/>
       </c>
       <c r="AF34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AF33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AF33)</f>
         <v/>
       </c>
       <c r="AG34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AG33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AG33)</f>
         <v/>
       </c>
       <c r="AH34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AH33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AH33)</f>
         <v/>
       </c>
       <c r="AI34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AI33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AI33)</f>
         <v/>
       </c>
       <c r="AJ34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AJ33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AJ33)</f>
         <v/>
       </c>
       <c r="AK34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AK33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AK33)</f>
         <v/>
       </c>
       <c r="AL34" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B34-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B34),AL33)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B34-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B34),AL33)</f>
         <v/>
       </c>
     </row>
@@ -4120,75 +4120,75 @@
       </c>
       <c r="P35" s="11" t="n"/>
       <c r="T35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),T34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),T34)</f>
         <v/>
       </c>
       <c r="U35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),U34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),U34)</f>
         <v/>
       </c>
       <c r="V35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),V34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),V34)</f>
         <v/>
       </c>
       <c r="W35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),W34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),W34)</f>
         <v/>
       </c>
       <c r="X35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),X34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),X34)</f>
         <v/>
       </c>
       <c r="Y35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),Y34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),Y34)</f>
         <v/>
       </c>
       <c r="Z35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),Z34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),Z34)</f>
         <v/>
       </c>
       <c r="AA35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AA34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AA34)</f>
         <v/>
       </c>
       <c r="AB35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AB34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AB34)</f>
         <v/>
       </c>
       <c r="AD35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AD34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AD34)</f>
         <v/>
       </c>
       <c r="AE35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AE34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AE34)</f>
         <v/>
       </c>
       <c r="AF35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AF34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AF34)</f>
         <v/>
       </c>
       <c r="AG35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AG34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AG34)</f>
         <v/>
       </c>
       <c r="AH35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AH34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AH34)</f>
         <v/>
       </c>
       <c r="AI35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AI34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AI34)</f>
         <v/>
       </c>
       <c r="AJ35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AJ34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AJ34)</f>
         <v/>
       </c>
       <c r="AK35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AK34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AK34)</f>
         <v/>
       </c>
       <c r="AL35" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B35-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B35),AL34)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B35-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B35),AL34)</f>
         <v/>
       </c>
     </row>
@@ -4234,75 +4234,75 @@
       <c r="O36" s="17" t="n"/>
       <c r="P36" s="11" t="n"/>
       <c r="T36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),T35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),T35)</f>
         <v/>
       </c>
       <c r="U36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),U35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),U35)</f>
         <v/>
       </c>
       <c r="V36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),V35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),V35)</f>
         <v/>
       </c>
       <c r="W36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),W35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),W35)</f>
         <v/>
       </c>
       <c r="X36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),X35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),X35)</f>
         <v/>
       </c>
       <c r="Y36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),Y35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),Y35)</f>
         <v/>
       </c>
       <c r="Z36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),Z35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),Z35)</f>
         <v/>
       </c>
       <c r="AA36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AA35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AA35)</f>
         <v/>
       </c>
       <c r="AB36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AB35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AB35)</f>
         <v/>
       </c>
       <c r="AD36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AD35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AD35)</f>
         <v/>
       </c>
       <c r="AE36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AE35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AE35)</f>
         <v/>
       </c>
       <c r="AF36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AF35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AF35)</f>
         <v/>
       </c>
       <c r="AG36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AG35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AG35)</f>
         <v/>
       </c>
       <c r="AH36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AH35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AH35)</f>
         <v/>
       </c>
       <c r="AI36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AI35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AI35)</f>
         <v/>
       </c>
       <c r="AJ36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AJ35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AJ35)</f>
         <v/>
       </c>
       <c r="AK36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AK35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AK35)</f>
         <v/>
       </c>
       <c r="AL36" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B36-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B36),AL35)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),AL35)</f>
         <v/>
       </c>
     </row>
@@ -4365,75 +4365,75 @@
         <v/>
       </c>
       <c r="T37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),T36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),T36)</f>
         <v/>
       </c>
       <c r="U37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),U36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),U36)</f>
         <v/>
       </c>
       <c r="V37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),V36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),V36)</f>
         <v/>
       </c>
       <c r="W37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),W36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),W36)</f>
         <v/>
       </c>
       <c r="X37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),X36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),X36)</f>
         <v/>
       </c>
       <c r="Y37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),Y36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),Y36)</f>
         <v/>
       </c>
       <c r="Z37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),Z36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),Z36)</f>
         <v/>
       </c>
       <c r="AA37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AA36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AA36)</f>
         <v/>
       </c>
       <c r="AB37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AB36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AB36)</f>
         <v/>
       </c>
       <c r="AD37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AD36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AD36)</f>
         <v/>
       </c>
       <c r="AE37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AE36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AE36)</f>
         <v/>
       </c>
       <c r="AF37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AF36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AF36)</f>
         <v/>
       </c>
       <c r="AG37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AG36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AG36)</f>
         <v/>
       </c>
       <c r="AH37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AH36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AH36)</f>
         <v/>
       </c>
       <c r="AI37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AI36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AI36)</f>
         <v/>
       </c>
       <c r="AJ37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AJ36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AJ36)</f>
         <v/>
       </c>
       <c r="AK37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AK36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AK36)</f>
         <v/>
       </c>
       <c r="AL37" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B37-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B37),AL36)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B37-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B37),AL36)</f>
         <v/>
       </c>
       <c r="AN37">
@@ -4504,75 +4504,75 @@
         <v/>
       </c>
       <c r="T38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),T37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),T37)</f>
         <v/>
       </c>
       <c r="U38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),U37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),U37)</f>
         <v/>
       </c>
       <c r="V38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),V37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),V37)</f>
         <v/>
       </c>
       <c r="W38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),W37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),W37)</f>
         <v/>
       </c>
       <c r="X38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),X37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),X37)</f>
         <v/>
       </c>
       <c r="Y38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),Y37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),Y37)</f>
         <v/>
       </c>
       <c r="Z38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),Z37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),Z37)</f>
         <v/>
       </c>
       <c r="AA38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AA37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AA37)</f>
         <v/>
       </c>
       <c r="AB38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AB37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AB37)</f>
         <v/>
       </c>
       <c r="AD38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AD37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AD37)</f>
         <v/>
       </c>
       <c r="AE38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AE37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AE37)</f>
         <v/>
       </c>
       <c r="AF38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AF37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AF37)</f>
         <v/>
       </c>
       <c r="AG38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AG37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AG37)</f>
         <v/>
       </c>
       <c r="AH38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AH37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AH37)</f>
         <v/>
       </c>
       <c r="AI38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AI37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AI37)</f>
         <v/>
       </c>
       <c r="AJ38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AJ37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AJ37)</f>
         <v/>
       </c>
       <c r="AK38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AK37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AK37)</f>
         <v/>
       </c>
       <c r="AL38" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B38-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B38),AL37)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B38-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B38),AL37)</f>
         <v/>
       </c>
       <c r="AN38">
@@ -4643,75 +4643,75 @@
         <v/>
       </c>
       <c r="T39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),T38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),T38)</f>
         <v/>
       </c>
       <c r="U39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),U38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),U38)</f>
         <v/>
       </c>
       <c r="V39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),V38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),V38)</f>
         <v/>
       </c>
       <c r="W39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),W38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),W38)</f>
         <v/>
       </c>
       <c r="X39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),X38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),X38)</f>
         <v/>
       </c>
       <c r="Y39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),Y38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),Y38)</f>
         <v/>
       </c>
       <c r="Z39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),Z38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),Z38)</f>
         <v/>
       </c>
       <c r="AA39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AA38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AA38)</f>
         <v/>
       </c>
       <c r="AB39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AB38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AB38)</f>
         <v/>
       </c>
       <c r="AD39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AD38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AD38)</f>
         <v/>
       </c>
       <c r="AE39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AE38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AE38)</f>
         <v/>
       </c>
       <c r="AF39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AF38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AF38)</f>
         <v/>
       </c>
       <c r="AG39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AG38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AG38)</f>
         <v/>
       </c>
       <c r="AH39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AH38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AH38)</f>
         <v/>
       </c>
       <c r="AI39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AI38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AI38)</f>
         <v/>
       </c>
       <c r="AJ39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AJ38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AJ38)</f>
         <v/>
       </c>
       <c r="AK39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AK38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AK38)</f>
         <v/>
       </c>
       <c r="AL39" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B39-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B39),AL38)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B39-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B39),AL38)</f>
         <v/>
       </c>
       <c r="AN39">
@@ -4782,75 +4782,75 @@
         <v/>
       </c>
       <c r="T40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),T39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),T39)</f>
         <v/>
       </c>
       <c r="U40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),U39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),U39)</f>
         <v/>
       </c>
       <c r="V40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),V39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),V39)</f>
         <v/>
       </c>
       <c r="W40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),W39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),W39)</f>
         <v/>
       </c>
       <c r="X40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),X39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),X39)</f>
         <v/>
       </c>
       <c r="Y40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),Y39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),Y39)</f>
         <v/>
       </c>
       <c r="Z40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),Z39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),Z39)</f>
         <v/>
       </c>
       <c r="AA40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AA39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AA39)</f>
         <v/>
       </c>
       <c r="AB40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AB39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AB39)</f>
         <v/>
       </c>
       <c r="AD40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AD39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AD39)</f>
         <v/>
       </c>
       <c r="AE40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AE39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AE39)</f>
         <v/>
       </c>
       <c r="AF40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AF39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AF39)</f>
         <v/>
       </c>
       <c r="AG40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AG39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AG39)</f>
         <v/>
       </c>
       <c r="AH40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AH39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AH39)</f>
         <v/>
       </c>
       <c r="AI40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AI39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AI39)</f>
         <v/>
       </c>
       <c r="AJ40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AJ39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AJ39)</f>
         <v/>
       </c>
       <c r="AK40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AK39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AK39)</f>
         <v/>
       </c>
       <c r="AL40" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B40-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B40),AL39)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B40-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B40),AL39)</f>
         <v/>
       </c>
       <c r="AN40">
@@ -4921,75 +4921,75 @@
         <v/>
       </c>
       <c r="T41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),T40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),T40)</f>
         <v/>
       </c>
       <c r="U41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),U40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),U40)</f>
         <v/>
       </c>
       <c r="V41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),V40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),V40)</f>
         <v/>
       </c>
       <c r="W41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),W40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),W40)</f>
         <v/>
       </c>
       <c r="X41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),X40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),X40)</f>
         <v/>
       </c>
       <c r="Y41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),Y40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),Y40)</f>
         <v/>
       </c>
       <c r="Z41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),Z40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),Z40)</f>
         <v/>
       </c>
       <c r="AA41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AA40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AA40)</f>
         <v/>
       </c>
       <c r="AB41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AB40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AB40)</f>
         <v/>
       </c>
       <c r="AD41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AD40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AD40)</f>
         <v/>
       </c>
       <c r="AE41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AE40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AE40)</f>
         <v/>
       </c>
       <c r="AF41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AF40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AF40)</f>
         <v/>
       </c>
       <c r="AG41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AG40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AG40)</f>
         <v/>
       </c>
       <c r="AH41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AH40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AH40)</f>
         <v/>
       </c>
       <c r="AI41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AI40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AI40)</f>
         <v/>
       </c>
       <c r="AJ41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AJ40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AJ40)</f>
         <v/>
       </c>
       <c r="AK41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AK40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AK40)</f>
         <v/>
       </c>
       <c r="AL41" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B41-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B41),AL40)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B41-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B41),AL40)</f>
         <v/>
       </c>
       <c r="AN41">
@@ -5060,75 +5060,75 @@
         <v/>
       </c>
       <c r="T42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),T41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),T41)</f>
         <v/>
       </c>
       <c r="U42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),U41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),U41)</f>
         <v/>
       </c>
       <c r="V42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),V41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),V41)</f>
         <v/>
       </c>
       <c r="W42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),W41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),W41)</f>
         <v/>
       </c>
       <c r="X42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),X41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),X41)</f>
         <v/>
       </c>
       <c r="Y42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),Y41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),Y41)</f>
         <v/>
       </c>
       <c r="Z42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),Z41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),Z41)</f>
         <v/>
       </c>
       <c r="AA42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AA41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AA41)</f>
         <v/>
       </c>
       <c r="AB42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AB41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AB41)</f>
         <v/>
       </c>
       <c r="AD42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AD41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AD41)</f>
         <v/>
       </c>
       <c r="AE42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AE41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AE41)</f>
         <v/>
       </c>
       <c r="AF42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AF41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AF41)</f>
         <v/>
       </c>
       <c r="AG42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AG41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AG41)</f>
         <v/>
       </c>
       <c r="AH42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AH41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AH41)</f>
         <v/>
       </c>
       <c r="AI42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AI41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AI41)</f>
         <v/>
       </c>
       <c r="AJ42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AJ41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AJ41)</f>
         <v/>
       </c>
       <c r="AK42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AK41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AK41)</f>
         <v/>
       </c>
       <c r="AL42" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B42-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B42),AL41)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B42-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B42),AL41)</f>
         <v/>
       </c>
       <c r="AN42">
@@ -5199,75 +5199,75 @@
         <v/>
       </c>
       <c r="T43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),T42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),T42)</f>
         <v/>
       </c>
       <c r="U43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),U42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),U42)</f>
         <v/>
       </c>
       <c r="V43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),V42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),V42)</f>
         <v/>
       </c>
       <c r="W43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),W42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),W42)</f>
         <v/>
       </c>
       <c r="X43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),X42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),X42)</f>
         <v/>
       </c>
       <c r="Y43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),Y42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),Y42)</f>
         <v/>
       </c>
       <c r="Z43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),Z42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),Z42)</f>
         <v/>
       </c>
       <c r="AA43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AA42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AA42)</f>
         <v/>
       </c>
       <c r="AB43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AB42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AB42)</f>
         <v/>
       </c>
       <c r="AD43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AD42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AD42)</f>
         <v/>
       </c>
       <c r="AE43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AE42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AE42)</f>
         <v/>
       </c>
       <c r="AF43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AF42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AF42)</f>
         <v/>
       </c>
       <c r="AG43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AG42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AG42)</f>
         <v/>
       </c>
       <c r="AH43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AH42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AH42)</f>
         <v/>
       </c>
       <c r="AI43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AI42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AI42)</f>
         <v/>
       </c>
       <c r="AJ43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AJ42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AJ42)</f>
         <v/>
       </c>
       <c r="AK43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AK42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AK42)</f>
         <v/>
       </c>
       <c r="AL43" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B43-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B43),AL42)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B43-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B43),AL42)</f>
         <v/>
       </c>
       <c r="AN43">
@@ -5338,75 +5338,75 @@
         <v/>
       </c>
       <c r="T44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),T43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),T43)</f>
         <v/>
       </c>
       <c r="U44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),U43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),U43)</f>
         <v/>
       </c>
       <c r="V44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),V43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),V43)</f>
         <v/>
       </c>
       <c r="W44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),W43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),W43)</f>
         <v/>
       </c>
       <c r="X44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),X43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),X43)</f>
         <v/>
       </c>
       <c r="Y44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),Y43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),Y43)</f>
         <v/>
       </c>
       <c r="Z44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),Z43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),Z43)</f>
         <v/>
       </c>
       <c r="AA44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AA43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AA43)</f>
         <v/>
       </c>
       <c r="AB44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AB43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AB43)</f>
         <v/>
       </c>
       <c r="AD44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AD43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AD43)</f>
         <v/>
       </c>
       <c r="AE44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AE43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AE43)</f>
         <v/>
       </c>
       <c r="AF44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AF43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AF43)</f>
         <v/>
       </c>
       <c r="AG44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AG43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AG43)</f>
         <v/>
       </c>
       <c r="AH44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AH43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AH43)</f>
         <v/>
       </c>
       <c r="AI44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AI43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AI43)</f>
         <v/>
       </c>
       <c r="AJ44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AJ43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AJ43)</f>
         <v/>
       </c>
       <c r="AK44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AK43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AK43)</f>
         <v/>
       </c>
       <c r="AL44" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B44-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B44),AL43)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B44-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B44),AL43)</f>
         <v/>
       </c>
       <c r="AN44">
@@ -5477,75 +5477,75 @@
         <v/>
       </c>
       <c r="T45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),T44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),T44)</f>
         <v/>
       </c>
       <c r="U45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),U44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),U44)</f>
         <v/>
       </c>
       <c r="V45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),V44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),V44)</f>
         <v/>
       </c>
       <c r="W45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),W44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),W44)</f>
         <v/>
       </c>
       <c r="X45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),X44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),X44)</f>
         <v/>
       </c>
       <c r="Y45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),Y44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),Y44)</f>
         <v/>
       </c>
       <c r="Z45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),Z44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),Z44)</f>
         <v/>
       </c>
       <c r="AA45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AA44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AA44)</f>
         <v/>
       </c>
       <c r="AB45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AB44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AB44)</f>
         <v/>
       </c>
       <c r="AD45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AD44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AD44)</f>
         <v/>
       </c>
       <c r="AE45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AE44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AE44)</f>
         <v/>
       </c>
       <c r="AF45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AF44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AF44)</f>
         <v/>
       </c>
       <c r="AG45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AG44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AG44)</f>
         <v/>
       </c>
       <c r="AH45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AH44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AH44)</f>
         <v/>
       </c>
       <c r="AI45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AI44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AI44)</f>
         <v/>
       </c>
       <c r="AJ45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AJ44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AJ44)</f>
         <v/>
       </c>
       <c r="AK45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AK44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AK44)</f>
         <v/>
       </c>
       <c r="AL45" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B45-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B45),AL44)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B45-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B45),AL44)</f>
         <v/>
       </c>
       <c r="AN45">
@@ -5616,75 +5616,75 @@
         <v/>
       </c>
       <c r="T46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),T45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),T45)</f>
         <v/>
       </c>
       <c r="U46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),U45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),U45)</f>
         <v/>
       </c>
       <c r="V46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),V45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),V45)</f>
         <v/>
       </c>
       <c r="W46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),W45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),W45)</f>
         <v/>
       </c>
       <c r="X46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),X45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),X45)</f>
         <v/>
       </c>
       <c r="Y46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),Y45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),Y45)</f>
         <v/>
       </c>
       <c r="Z46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),Z45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),Z45)</f>
         <v/>
       </c>
       <c r="AA46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AA45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AA45)</f>
         <v/>
       </c>
       <c r="AB46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AB45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AB45)</f>
         <v/>
       </c>
       <c r="AD46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AD45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AD45)</f>
         <v/>
       </c>
       <c r="AE46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AE45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AE45)</f>
         <v/>
       </c>
       <c r="AF46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AF45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AF45)</f>
         <v/>
       </c>
       <c r="AG46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AG45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AG45)</f>
         <v/>
       </c>
       <c r="AH46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AH45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AH45)</f>
         <v/>
       </c>
       <c r="AI46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AI45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AI45)</f>
         <v/>
       </c>
       <c r="AJ46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AJ45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AJ45)</f>
         <v/>
       </c>
       <c r="AK46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AK45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AK45)</f>
         <v/>
       </c>
       <c r="AL46" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B46-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B46),AL45)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B46-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B46),AL45)</f>
         <v/>
       </c>
       <c r="AN46">
@@ -5755,75 +5755,75 @@
         <v/>
       </c>
       <c r="T47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),T46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),T46)</f>
         <v/>
       </c>
       <c r="U47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),U46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),U46)</f>
         <v/>
       </c>
       <c r="V47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),V46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),V46)</f>
         <v/>
       </c>
       <c r="W47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),W46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),W46)</f>
         <v/>
       </c>
       <c r="X47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),X46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),X46)</f>
         <v/>
       </c>
       <c r="Y47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),Y46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),Y46)</f>
         <v/>
       </c>
       <c r="Z47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),Z46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),Z46)</f>
         <v/>
       </c>
       <c r="AA47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AA46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AA46)</f>
         <v/>
       </c>
       <c r="AB47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AB46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AB46)</f>
         <v/>
       </c>
       <c r="AD47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AD46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AD46)</f>
         <v/>
       </c>
       <c r="AE47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AE46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AE46)</f>
         <v/>
       </c>
       <c r="AF47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AF46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AF46)</f>
         <v/>
       </c>
       <c r="AG47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AG46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AG46)</f>
         <v/>
       </c>
       <c r="AH47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AH46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AH46)</f>
         <v/>
       </c>
       <c r="AI47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AI46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AI46)</f>
         <v/>
       </c>
       <c r="AJ47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AJ46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AJ46)</f>
         <v/>
       </c>
       <c r="AK47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AK46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AK46)</f>
         <v/>
       </c>
       <c r="AL47" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B47-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B47),AL46)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B47-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B47),AL46)</f>
         <v/>
       </c>
       <c r="AN47">
@@ -5894,75 +5894,75 @@
         <v/>
       </c>
       <c r="T48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),T47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),T47)</f>
         <v/>
       </c>
       <c r="U48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),U47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),U47)</f>
         <v/>
       </c>
       <c r="V48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),V47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),V47)</f>
         <v/>
       </c>
       <c r="W48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),W47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),W47)</f>
         <v/>
       </c>
       <c r="X48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),X47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),X47)</f>
         <v/>
       </c>
       <c r="Y48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),Y47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),Y47)</f>
         <v/>
       </c>
       <c r="Z48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),Z47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),Z47)</f>
         <v/>
       </c>
       <c r="AA48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AA47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AA47)</f>
         <v/>
       </c>
       <c r="AB48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AB47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AB47)</f>
         <v/>
       </c>
       <c r="AD48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AD47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AD47)</f>
         <v/>
       </c>
       <c r="AE48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AE47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AE47)</f>
         <v/>
       </c>
       <c r="AF48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AF47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AF47)</f>
         <v/>
       </c>
       <c r="AG48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AG47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AG47)</f>
         <v/>
       </c>
       <c r="AH48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AH47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AH47)</f>
         <v/>
       </c>
       <c r="AI48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AI47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AI47)</f>
         <v/>
       </c>
       <c r="AJ48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AJ47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AJ47)</f>
         <v/>
       </c>
       <c r="AK48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AK47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AK47)</f>
         <v/>
       </c>
       <c r="AL48" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B48-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B48),AL47)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B48-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B48),AL47)</f>
         <v/>
       </c>
       <c r="AN48">
@@ -6033,75 +6033,75 @@
         <v/>
       </c>
       <c r="T49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),T48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),T48)</f>
         <v/>
       </c>
       <c r="U49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),U48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),U48)</f>
         <v/>
       </c>
       <c r="V49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),V48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),V48)</f>
         <v/>
       </c>
       <c r="W49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),W48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),W48)</f>
         <v/>
       </c>
       <c r="X49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),X48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),X48)</f>
         <v/>
       </c>
       <c r="Y49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),Y48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),Y48)</f>
         <v/>
       </c>
       <c r="Z49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),Z48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),Z48)</f>
         <v/>
       </c>
       <c r="AA49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AA48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AA48)</f>
         <v/>
       </c>
       <c r="AB49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AB48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AB48)</f>
         <v/>
       </c>
       <c r="AD49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AD48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AD48)</f>
         <v/>
       </c>
       <c r="AE49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AE48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AE48)</f>
         <v/>
       </c>
       <c r="AF49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AF48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AF48)</f>
         <v/>
       </c>
       <c r="AG49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AG48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AG48)</f>
         <v/>
       </c>
       <c r="AH49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AH48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AH48)</f>
         <v/>
       </c>
       <c r="AI49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AI48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AI48)</f>
         <v/>
       </c>
       <c r="AJ49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AJ48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AJ48)</f>
         <v/>
       </c>
       <c r="AK49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AK48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AK48)</f>
         <v/>
       </c>
       <c r="AL49" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B49-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B49),AL48)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B49-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B49),AL48)</f>
         <v/>
       </c>
       <c r="AN49">
@@ -6172,75 +6172,75 @@
         <v/>
       </c>
       <c r="T50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),T49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),T49)</f>
         <v/>
       </c>
       <c r="U50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),U49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),U49)</f>
         <v/>
       </c>
       <c r="V50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),V49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),V49)</f>
         <v/>
       </c>
       <c r="W50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),W49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),W49)</f>
         <v/>
       </c>
       <c r="X50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),X49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),X49)</f>
         <v/>
       </c>
       <c r="Y50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),Y49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),Y49)</f>
         <v/>
       </c>
       <c r="Z50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),Z49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),Z49)</f>
         <v/>
       </c>
       <c r="AA50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AA49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AA49)</f>
         <v/>
       </c>
       <c r="AB50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AB49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AB49)</f>
         <v/>
       </c>
       <c r="AD50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AD49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AD49)</f>
         <v/>
       </c>
       <c r="AE50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AE49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AE49)</f>
         <v/>
       </c>
       <c r="AF50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AF49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AF49)</f>
         <v/>
       </c>
       <c r="AG50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AG49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AG49)</f>
         <v/>
       </c>
       <c r="AH50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AH49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AH49)</f>
         <v/>
       </c>
       <c r="AI50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AI49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AI49)</f>
         <v/>
       </c>
       <c r="AJ50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AJ49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AJ49)</f>
         <v/>
       </c>
       <c r="AK50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AK49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AK49)</f>
         <v/>
       </c>
       <c r="AL50" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B50-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B50),AL49)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B50-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B50),AL49)</f>
         <v/>
       </c>
       <c r="AN50">
@@ -6311,75 +6311,75 @@
         <v/>
       </c>
       <c r="T51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),T50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),T50)</f>
         <v/>
       </c>
       <c r="U51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),U50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),U50)</f>
         <v/>
       </c>
       <c r="V51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),V50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),V50)</f>
         <v/>
       </c>
       <c r="W51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),W50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),W50)</f>
         <v/>
       </c>
       <c r="X51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),X50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),X50)</f>
         <v/>
       </c>
       <c r="Y51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),Y50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),Y50)</f>
         <v/>
       </c>
       <c r="Z51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),Z50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),Z50)</f>
         <v/>
       </c>
       <c r="AA51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AA50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AA50)</f>
         <v/>
       </c>
       <c r="AB51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AB50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AB50)</f>
         <v/>
       </c>
       <c r="AD51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AD50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AD50)</f>
         <v/>
       </c>
       <c r="AE51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AE50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AE50)</f>
         <v/>
       </c>
       <c r="AF51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AF50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AF50)</f>
         <v/>
       </c>
       <c r="AG51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AG50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AG50)</f>
         <v/>
       </c>
       <c r="AH51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AH50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AH50)</f>
         <v/>
       </c>
       <c r="AI51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AI50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AI50)</f>
         <v/>
       </c>
       <c r="AJ51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AJ50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AJ50)</f>
         <v/>
       </c>
       <c r="AK51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AK50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AK50)</f>
         <v/>
       </c>
       <c r="AL51" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B51-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B51),AL50)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B51-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B51),AL50)</f>
         <v/>
       </c>
       <c r="AN51">
@@ -6450,75 +6450,75 @@
         <v/>
       </c>
       <c r="T52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),T51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),T51)</f>
         <v/>
       </c>
       <c r="U52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),U51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),U51)</f>
         <v/>
       </c>
       <c r="V52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),V51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),V51)</f>
         <v/>
       </c>
       <c r="W52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),W51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),W51)</f>
         <v/>
       </c>
       <c r="X52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),X51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),X51)</f>
         <v/>
       </c>
       <c r="Y52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),Y51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),Y51)</f>
         <v/>
       </c>
       <c r="Z52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),Z51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),Z51)</f>
         <v/>
       </c>
       <c r="AA52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AA51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AA51)</f>
         <v/>
       </c>
       <c r="AB52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AB51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AB51)</f>
         <v/>
       </c>
       <c r="AD52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AD51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AD51)</f>
         <v/>
       </c>
       <c r="AE52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AE51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AE51)</f>
         <v/>
       </c>
       <c r="AF52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AF51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AF51)</f>
         <v/>
       </c>
       <c r="AG52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AG51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AG51)</f>
         <v/>
       </c>
       <c r="AH52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AH51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AH51)</f>
         <v/>
       </c>
       <c r="AI52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AI51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AI51)</f>
         <v/>
       </c>
       <c r="AJ52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AJ51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AJ51)</f>
         <v/>
       </c>
       <c r="AK52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AK51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AK51)</f>
         <v/>
       </c>
       <c r="AL52" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B52-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B52),AL51)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B52-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B52),AL51)</f>
         <v/>
       </c>
       <c r="AN52">
@@ -6589,75 +6589,75 @@
         <v/>
       </c>
       <c r="T53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),T52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),T52)</f>
         <v/>
       </c>
       <c r="U53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),U52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),U52)</f>
         <v/>
       </c>
       <c r="V53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),V52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),V52)</f>
         <v/>
       </c>
       <c r="W53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),W52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),W52)</f>
         <v/>
       </c>
       <c r="X53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),X52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),X52)</f>
         <v/>
       </c>
       <c r="Y53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),Y52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),Y52)</f>
         <v/>
       </c>
       <c r="Z53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),Z52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),Z52)</f>
         <v/>
       </c>
       <c r="AA53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AA52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AA52)</f>
         <v/>
       </c>
       <c r="AB53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AB52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AB52)</f>
         <v/>
       </c>
       <c r="AD53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AD52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AD52)</f>
         <v/>
       </c>
       <c r="AE53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AE52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AE52)</f>
         <v/>
       </c>
       <c r="AF53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AF52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AF52)</f>
         <v/>
       </c>
       <c r="AG53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AG52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AG52)</f>
         <v/>
       </c>
       <c r="AH53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AH52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AH52)</f>
         <v/>
       </c>
       <c r="AI53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AI52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AI52)</f>
         <v/>
       </c>
       <c r="AJ53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AJ52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AJ52)</f>
         <v/>
       </c>
       <c r="AK53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AK52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AK52)</f>
         <v/>
       </c>
       <c r="AL53" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B53-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B53),AL52)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B53-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B53),AL52)</f>
         <v/>
       </c>
       <c r="AN53">
@@ -6728,75 +6728,75 @@
         <v/>
       </c>
       <c r="T54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),T53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),T53)</f>
         <v/>
       </c>
       <c r="U54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),U53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),U53)</f>
         <v/>
       </c>
       <c r="V54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),V53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),V53)</f>
         <v/>
       </c>
       <c r="W54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),W53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),W53)</f>
         <v/>
       </c>
       <c r="X54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),X53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),X53)</f>
         <v/>
       </c>
       <c r="Y54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),Y53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),Y53)</f>
         <v/>
       </c>
       <c r="Z54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),Z53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),Z53)</f>
         <v/>
       </c>
       <c r="AA54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AA53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AA53)</f>
         <v/>
       </c>
       <c r="AB54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AB53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AB53)</f>
         <v/>
       </c>
       <c r="AD54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AD53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AD53)</f>
         <v/>
       </c>
       <c r="AE54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AE53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AE53)</f>
         <v/>
       </c>
       <c r="AF54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AF53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AF53)</f>
         <v/>
       </c>
       <c r="AG54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AG53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AG53)</f>
         <v/>
       </c>
       <c r="AH54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AH53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AH53)</f>
         <v/>
       </c>
       <c r="AI54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AI53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AI53)</f>
         <v/>
       </c>
       <c r="AJ54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AJ53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AJ53)</f>
         <v/>
       </c>
       <c r="AK54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AK53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AK53)</f>
         <v/>
       </c>
       <c r="AL54" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B54-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B54),AL53)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B54-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B54),AL53)</f>
         <v/>
       </c>
       <c r="AN54">
@@ -6867,75 +6867,75 @@
         <v/>
       </c>
       <c r="T55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),T54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),T54)</f>
         <v/>
       </c>
       <c r="U55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),U54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),U54)</f>
         <v/>
       </c>
       <c r="V55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),V54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),V54)</f>
         <v/>
       </c>
       <c r="W55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),W54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),W54)</f>
         <v/>
       </c>
       <c r="X55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),X54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),X54)</f>
         <v/>
       </c>
       <c r="Y55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),Y54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),Y54)</f>
         <v/>
       </c>
       <c r="Z55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),Z54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),Z54)</f>
         <v/>
       </c>
       <c r="AA55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AA54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AA54)</f>
         <v/>
       </c>
       <c r="AB55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AB54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AB54)</f>
         <v/>
       </c>
       <c r="AD55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AD54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AD54)</f>
         <v/>
       </c>
       <c r="AE55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AE54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AE54)</f>
         <v/>
       </c>
       <c r="AF55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AF54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AF54)</f>
         <v/>
       </c>
       <c r="AG55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AG54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AG54)</f>
         <v/>
       </c>
       <c r="AH55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AH54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AH54)</f>
         <v/>
       </c>
       <c r="AI55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AI54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AI54)</f>
         <v/>
       </c>
       <c r="AJ55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AJ54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AJ54)</f>
         <v/>
       </c>
       <c r="AK55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AK54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AK54)</f>
         <v/>
       </c>
       <c r="AL55" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B55-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B55),AL54)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B55-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B55),AL54)</f>
         <v/>
       </c>
       <c r="AN55">
@@ -7006,75 +7006,75 @@
         <v/>
       </c>
       <c r="T56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),T55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),T55)</f>
         <v/>
       </c>
       <c r="U56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),U55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),U55)</f>
         <v/>
       </c>
       <c r="V56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),V55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),V55)</f>
         <v/>
       </c>
       <c r="W56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),W55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),W55)</f>
         <v/>
       </c>
       <c r="X56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),X55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),X55)</f>
         <v/>
       </c>
       <c r="Y56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),Y55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),Y55)</f>
         <v/>
       </c>
       <c r="Z56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),Z55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),Z55)</f>
         <v/>
       </c>
       <c r="AA56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AA55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AA55)</f>
         <v/>
       </c>
       <c r="AB56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AB55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AB55)</f>
         <v/>
       </c>
       <c r="AD56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AD55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AD55)</f>
         <v/>
       </c>
       <c r="AE56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AE55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AE55)</f>
         <v/>
       </c>
       <c r="AF56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AF55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AF55)</f>
         <v/>
       </c>
       <c r="AG56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AG55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AG55)</f>
         <v/>
       </c>
       <c r="AH56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AH55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AH55)</f>
         <v/>
       </c>
       <c r="AI56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AI55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AI55)</f>
         <v/>
       </c>
       <c r="AJ56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AJ55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AJ55)</f>
         <v/>
       </c>
       <c r="AK56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AK55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AK55)</f>
         <v/>
       </c>
       <c r="AL56" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B56-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B56),AL55)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B56-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B56),AL55)</f>
         <v/>
       </c>
       <c r="AN56">
@@ -7145,75 +7145,75 @@
         <v/>
       </c>
       <c r="T57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),T56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),T56)</f>
         <v/>
       </c>
       <c r="U57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),U56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),U56)</f>
         <v/>
       </c>
       <c r="V57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),V56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),V56)</f>
         <v/>
       </c>
       <c r="W57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),W56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),W56)</f>
         <v/>
       </c>
       <c r="X57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),X56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),X56)</f>
         <v/>
       </c>
       <c r="Y57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),Y56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),Y56)</f>
         <v/>
       </c>
       <c r="Z57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),Z56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),Z56)</f>
         <v/>
       </c>
       <c r="AA57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AA56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AA56)</f>
         <v/>
       </c>
       <c r="AB57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AB56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AB56)</f>
         <v/>
       </c>
       <c r="AD57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AD56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AD56)</f>
         <v/>
       </c>
       <c r="AE57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AE56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AE56)</f>
         <v/>
       </c>
       <c r="AF57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AF56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AF56)</f>
         <v/>
       </c>
       <c r="AG57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AG56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AG56)</f>
         <v/>
       </c>
       <c r="AH57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AH56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AH56)</f>
         <v/>
       </c>
       <c r="AI57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AI56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AI56)</f>
         <v/>
       </c>
       <c r="AJ57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AJ56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AJ56)</f>
         <v/>
       </c>
       <c r="AK57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AK56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AK56)</f>
         <v/>
       </c>
       <c r="AL57" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B57-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B57),AL56)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B57-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B57),AL56)</f>
         <v/>
       </c>
       <c r="AN57">
@@ -7284,75 +7284,75 @@
         <v/>
       </c>
       <c r="T58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),T57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),T57)</f>
         <v/>
       </c>
       <c r="U58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),U57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),U57)</f>
         <v/>
       </c>
       <c r="V58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),V57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),V57)</f>
         <v/>
       </c>
       <c r="W58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),W57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),W57)</f>
         <v/>
       </c>
       <c r="X58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),X57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),X57)</f>
         <v/>
       </c>
       <c r="Y58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),Y57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),Y57)</f>
         <v/>
       </c>
       <c r="Z58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),Z57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),Z57)</f>
         <v/>
       </c>
       <c r="AA58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AA57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AA57)</f>
         <v/>
       </c>
       <c r="AB58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AB57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AB57)</f>
         <v/>
       </c>
       <c r="AD58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AD57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AD57)</f>
         <v/>
       </c>
       <c r="AE58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AE57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AE57)</f>
         <v/>
       </c>
       <c r="AF58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AF57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AF57)</f>
         <v/>
       </c>
       <c r="AG58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AG57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AG57)</f>
         <v/>
       </c>
       <c r="AH58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AH57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AH57)</f>
         <v/>
       </c>
       <c r="AI58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AI57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AI57)</f>
         <v/>
       </c>
       <c r="AJ58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AJ57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AJ57)</f>
         <v/>
       </c>
       <c r="AK58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AK57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AK57)</f>
         <v/>
       </c>
       <c r="AL58" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B58-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B58),AL57)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B58-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B58),AL57)</f>
         <v/>
       </c>
       <c r="AN58">
@@ -7423,75 +7423,75 @@
         <v/>
       </c>
       <c r="T59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),T58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),T58)</f>
         <v/>
       </c>
       <c r="U59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),U58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),U58)</f>
         <v/>
       </c>
       <c r="V59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),V58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),V58)</f>
         <v/>
       </c>
       <c r="W59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),W58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),W58)</f>
         <v/>
       </c>
       <c r="X59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),X58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),X58)</f>
         <v/>
       </c>
       <c r="Y59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),Y58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),Y58)</f>
         <v/>
       </c>
       <c r="Z59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),Z58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),Z58)</f>
         <v/>
       </c>
       <c r="AA59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AA58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AA58)</f>
         <v/>
       </c>
       <c r="AB59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AB58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AB58)</f>
         <v/>
       </c>
       <c r="AD59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AD58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AD58)</f>
         <v/>
       </c>
       <c r="AE59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AE58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AE58)</f>
         <v/>
       </c>
       <c r="AF59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AF58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AF58)</f>
         <v/>
       </c>
       <c r="AG59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AG58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AG58)</f>
         <v/>
       </c>
       <c r="AH59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AH58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AH58)</f>
         <v/>
       </c>
       <c r="AI59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AI58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AI58)</f>
         <v/>
       </c>
       <c r="AJ59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AJ58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AJ58)</f>
         <v/>
       </c>
       <c r="AK59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AK58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AK58)</f>
         <v/>
       </c>
       <c r="AL59" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B59-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B59),AL58)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B59-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B59),AL58)</f>
         <v/>
       </c>
       <c r="AN59">
@@ -7562,75 +7562,75 @@
         <v/>
       </c>
       <c r="T60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),T59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),T59)</f>
         <v/>
       </c>
       <c r="U60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),U59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),U59)</f>
         <v/>
       </c>
       <c r="V60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),V59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),V59)</f>
         <v/>
       </c>
       <c r="W60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),W59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),W59)</f>
         <v/>
       </c>
       <c r="X60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),X59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),X59)</f>
         <v/>
       </c>
       <c r="Y60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),Y59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),Y59)</f>
         <v/>
       </c>
       <c r="Z60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),Z59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),Z59)</f>
         <v/>
       </c>
       <c r="AA60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AA59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AA59)</f>
         <v/>
       </c>
       <c r="AB60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AB59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AB59)</f>
         <v/>
       </c>
       <c r="AD60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AD59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AD59)</f>
         <v/>
       </c>
       <c r="AE60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AE59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AE59)</f>
         <v/>
       </c>
       <c r="AF60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AF59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AF59)</f>
         <v/>
       </c>
       <c r="AG60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AG59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AG59)</f>
         <v/>
       </c>
       <c r="AH60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AH59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AH59)</f>
         <v/>
       </c>
       <c r="AI60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AI59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AI59)</f>
         <v/>
       </c>
       <c r="AJ60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AJ59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AJ59)</f>
         <v/>
       </c>
       <c r="AK60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AK59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AK59)</f>
         <v/>
       </c>
       <c r="AL60" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B60-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B60),AL59)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B60-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B60),AL59)</f>
         <v/>
       </c>
       <c r="AN60">
@@ -7701,75 +7701,75 @@
         <v/>
       </c>
       <c r="T61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),T60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),T60)</f>
         <v/>
       </c>
       <c r="U61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),U60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),U60)</f>
         <v/>
       </c>
       <c r="V61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),V60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),V60)</f>
         <v/>
       </c>
       <c r="W61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),W60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),W60)</f>
         <v/>
       </c>
       <c r="X61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),X60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),X60)</f>
         <v/>
       </c>
       <c r="Y61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),Y60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),Y60)</f>
         <v/>
       </c>
       <c r="Z61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),Z60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),Z60)</f>
         <v/>
       </c>
       <c r="AA61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AA60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AA60)</f>
         <v/>
       </c>
       <c r="AB61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AB60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AB60)</f>
         <v/>
       </c>
       <c r="AD61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AD60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AD60)</f>
         <v/>
       </c>
       <c r="AE61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AE60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AE60)</f>
         <v/>
       </c>
       <c r="AF61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AF60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AF60)</f>
         <v/>
       </c>
       <c r="AG61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AG60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AG60)</f>
         <v/>
       </c>
       <c r="AH61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AH60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AH60)</f>
         <v/>
       </c>
       <c r="AI61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AI60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AI60)</f>
         <v/>
       </c>
       <c r="AJ61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AJ60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AJ60)</f>
         <v/>
       </c>
       <c r="AK61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AK60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AK60)</f>
         <v/>
       </c>
       <c r="AL61" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B61-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B61),AL60)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B61-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B61),AL60)</f>
         <v/>
       </c>
       <c r="AN61">
@@ -7840,75 +7840,75 @@
         <v/>
       </c>
       <c r="T62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),T61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),T61)</f>
         <v/>
       </c>
       <c r="U62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),U61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),U61)</f>
         <v/>
       </c>
       <c r="V62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),V61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),V61)</f>
         <v/>
       </c>
       <c r="W62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),W61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),W61)</f>
         <v/>
       </c>
       <c r="X62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),X61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),X61)</f>
         <v/>
       </c>
       <c r="Y62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),Y61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),Y61)</f>
         <v/>
       </c>
       <c r="Z62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),Z61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),Z61)</f>
         <v/>
       </c>
       <c r="AA62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AA61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AA61)</f>
         <v/>
       </c>
       <c r="AB62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AB61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AB61)</f>
         <v/>
       </c>
       <c r="AD62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AD61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AD61)</f>
         <v/>
       </c>
       <c r="AE62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AE61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AE61)</f>
         <v/>
       </c>
       <c r="AF62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AF61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AF61)</f>
         <v/>
       </c>
       <c r="AG62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AG61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AG61)</f>
         <v/>
       </c>
       <c r="AH62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AH61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AH61)</f>
         <v/>
       </c>
       <c r="AI62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AI61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AI61)</f>
         <v/>
       </c>
       <c r="AJ62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AJ61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AJ61)</f>
         <v/>
       </c>
       <c r="AK62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AK61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AK61)</f>
         <v/>
       </c>
       <c r="AL62" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B62-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B62),AL61)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B62-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B62),AL61)</f>
         <v/>
       </c>
       <c r="AN62">
@@ -7979,75 +7979,75 @@
         <v/>
       </c>
       <c r="T63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),T62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),T62)</f>
         <v/>
       </c>
       <c r="U63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),U62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),U62)</f>
         <v/>
       </c>
       <c r="V63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),V62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),V62)</f>
         <v/>
       </c>
       <c r="W63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),W62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),W62)</f>
         <v/>
       </c>
       <c r="X63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),X62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),X62)</f>
         <v/>
       </c>
       <c r="Y63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),Y62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),Y62)</f>
         <v/>
       </c>
       <c r="Z63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),Z62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),Z62)</f>
         <v/>
       </c>
       <c r="AA63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AA62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AA62)</f>
         <v/>
       </c>
       <c r="AB63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Asking Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AB62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AB62)</f>
         <v/>
       </c>
       <c r="AD63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],C$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AD62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AD62)</f>
         <v/>
       </c>
       <c r="AE63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],D$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AE62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,D$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AE62)</f>
         <v/>
       </c>
       <c r="AF63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],E$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AF62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,E$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AF62)</f>
         <v/>
       </c>
       <c r="AG63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],F$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AG62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,F$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AG62)</f>
         <v/>
       </c>
       <c r="AH63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],G$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AH62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,G$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AH62)</f>
         <v/>
       </c>
       <c r="AI63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],H$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AI62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,H$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AI62)</f>
         <v/>
       </c>
       <c r="AJ63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],I$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AJ62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,I$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AJ62)</f>
         <v/>
       </c>
       <c r="AK63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],J$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AK62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,J$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AK62)</f>
         <v/>
       </c>
       <c r="AL63" s="18">
-        <f>IF(COUNTIFS(HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63)&gt;0,AVERAGEIFS(HDUnitLevel[Last Effective Rent],HDUnitLevel[Floorplan Mapped],K$7,HDUnitLevel[Off Market Date],"&gt;="&amp;$B63-90,HDUnitLevel[Off Market Date],"&lt;="&amp;$B63),AL62)</f>
+        <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63)&gt;0,AVERAGEIFS('HD Dump'!$O$2:$O$538,'HD Dump'!$U$2:$U$538,K$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B63-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B63),AL62)</f>
         <v/>
       </c>
       <c r="AN63">

--- a/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
+++ b/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
@@ -3164,7 +3164,7 @@
         <v/>
       </c>
       <c r="I27" s="14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27" s="15" t="n">
         <v>3</v>
@@ -3280,7 +3280,7 @@
         <v/>
       </c>
       <c r="I28" s="14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>4</v>
@@ -3408,7 +3408,7 @@
       <c r="M29" s="11" t="n"/>
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="17" t="n">
-        <v>0</v>
+        <v>0.02406738868832729</v>
       </c>
       <c r="P29" s="11" t="n"/>
       <c r="T29" s="18">
@@ -3868,7 +3868,7 @@
         <v/>
       </c>
       <c r="I33" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J33" s="15" t="n">
         <v>10</v>
@@ -3986,7 +3986,7 @@
         <v/>
       </c>
       <c r="I34" s="14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>13</v>
@@ -4104,7 +4104,7 @@
         <v/>
       </c>
       <c r="I35" s="14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J35" s="15" t="n">
         <v>10</v>
@@ -4222,11 +4222,11 @@
         <v/>
       </c>
       <c r="I36" s="14" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J36" s="15" t="n"/>
       <c r="K36" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L36" s="16" t="n"/>
       <c r="M36" s="11" t="n"/>

--- a/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
+++ b/SeasonsMeridian/analysis/lease-up/Lease-Up Bridge (drop into model).xlsx
@@ -2822,16 +2822,12 @@
       <c r="I24" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="J24" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J24" s="15" t="n"/>
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="16" t="n"/>
       <c r="M24" s="11" t="n"/>
       <c r="N24" s="11" t="n"/>
-      <c r="O24" s="17" t="n">
-        <v>0.01433691756272393</v>
-      </c>
+      <c r="O24" s="17" t="n"/>
       <c r="P24" s="11" t="n"/>
       <c r="T24" s="18">
         <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B24-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B24),T23)</f>
@@ -3050,16 +3046,12 @@
       <c r="I26" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="J26" s="15" t="n">
-        <v>2</v>
-      </c>
+      <c r="J26" s="15" t="n"/>
       <c r="K26" s="14" t="n"/>
       <c r="L26" s="16" t="n"/>
       <c r="M26" s="11" t="n"/>
       <c r="N26" s="11" t="n"/>
-      <c r="O26" s="17" t="n">
-        <v>0.009025270758122761</v>
-      </c>
+      <c r="O26" s="17" t="n"/>
       <c r="P26" s="11" t="n"/>
       <c r="T26" s="18">
         <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B26-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B26),T25)</f>
@@ -3166,16 +3158,12 @@
       <c r="I27" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="J27" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="J27" s="15" t="n"/>
       <c r="K27" s="14" t="n"/>
       <c r="L27" s="16" t="n"/>
       <c r="M27" s="11" t="n"/>
       <c r="N27" s="11" t="n"/>
-      <c r="O27" s="17" t="n">
-        <v>-0.01811230585424136</v>
-      </c>
+      <c r="O27" s="17" t="n"/>
       <c r="P27" s="11" t="n"/>
       <c r="T27" s="18">
         <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B27-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B27),T26)</f>
@@ -3282,16 +3270,12 @@
       <c r="I28" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="J28" s="15" t="n">
-        <v>4</v>
-      </c>
+      <c r="J28" s="15" t="n"/>
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="16" t="n"/>
       <c r="M28" s="11" t="n"/>
       <c r="N28" s="11" t="n"/>
-      <c r="O28" s="17" t="n">
-        <v>0.01034402020303382</v>
-      </c>
+      <c r="O28" s="17" t="n"/>
       <c r="P28" s="11" t="n"/>
       <c r="T28" s="18">
         <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B28-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B28),T27)</f>
@@ -3399,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="14" t="n">
         <v>8</v>
@@ -3526,7 +3510,7 @@
       <c r="M30" s="11" t="n"/>
       <c r="N30" s="11" t="n"/>
       <c r="O30" s="17" t="n">
-        <v>0.02694567613411691</v>
+        <v>0.02694567613411694</v>
       </c>
       <c r="P30" s="11" t="n"/>
       <c r="T30" s="18">
@@ -3644,7 +3628,7 @@
       <c r="M31" s="11" t="n"/>
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="17" t="n">
-        <v>0.002170138888888876</v>
+        <v>0.002170138888888889</v>
       </c>
       <c r="P31" s="11" t="n"/>
       <c r="T31" s="18">
@@ -3762,7 +3746,7 @@
       <c r="M32" s="11" t="n"/>
       <c r="N32" s="11" t="n"/>
       <c r="O32" s="17" t="n">
-        <v>0.0179975358002076</v>
+        <v>0.01799753580020763</v>
       </c>
       <c r="P32" s="11" t="n"/>
       <c r="T32" s="18">
@@ -3868,7 +3852,7 @@
         <v/>
       </c>
       <c r="I33" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J33" s="15" t="n">
         <v>10</v>
@@ -3880,7 +3864,7 @@
       <c r="M33" s="11" t="n"/>
       <c r="N33" s="11" t="n"/>
       <c r="O33" s="17" t="n">
-        <v>0.02122619178528184</v>
+        <v>0.02122619178528182</v>
       </c>
       <c r="P33" s="11" t="n"/>
       <c r="T33" s="18">
@@ -3986,7 +3970,7 @@
         <v/>
       </c>
       <c r="I34" s="14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>13</v>
@@ -3998,7 +3982,7 @@
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>0.01665786423821667</v>
+        <v>0.0166578642382167</v>
       </c>
       <c r="P34" s="11" t="n"/>
       <c r="T34" s="18">
@@ -4104,10 +4088,10 @@
         <v/>
       </c>
       <c r="I35" s="14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K35" s="14" t="n">
         <v>27</v>
@@ -4116,7 +4100,7 @@
       <c r="M35" s="11" t="n"/>
       <c r="N35" s="11" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>0.02451694198814301</v>
+        <v>0.02130613513017518</v>
       </c>
       <c r="P35" s="11" t="n"/>
       <c r="T35" s="18">
@@ -4222,16 +4206,20 @@
         <v/>
       </c>
       <c r="I36" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="15" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="J36" s="15" t="n">
+        <v>9</v>
+      </c>
       <c r="K36" s="14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L36" s="16" t="n"/>
       <c r="M36" s="11" t="n"/>
       <c r="N36" s="11" t="n"/>
-      <c r="O36" s="17" t="n"/>
+      <c r="O36" s="17" t="n">
+        <v>0.03388435903977594</v>
+      </c>
       <c r="P36" s="11" t="n"/>
       <c r="T36" s="18">
         <f>IF(COUNTIFS('HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36)&gt;0,AVERAGEIFS('HD Dump'!$M$2:$M$538,'HD Dump'!$U$2:$U$538,C$7,'HD Dump'!$R$2:$R$538,"&gt;="&amp;$B36-90,'HD Dump'!$R$2:$R$538,"&lt;="&amp;$B36),T35)</f>
